--- a/data/trans_orig/P57B2_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P57B2_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según se ha sentido feliz en 2023</t>
+          <t>Población según se ha sentido feliz en 2023 (tasa de respuesta: 99,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>265210</t>
+          <t>266015</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>321768</t>
+          <t>319953</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>257246</t>
+          <t>259462</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>299826</t>
+          <t>300611</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>534213</t>
+          <t>537907</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>603565</t>
+          <t>606901</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,6%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>199890</t>
+          <t>199756</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>248328</t>
+          <t>249486</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>238894</t>
+          <t>238098</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>279061</t>
+          <t>275698</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>449936</t>
+          <t>451168</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>514141</t>
+          <t>512366</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,34%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76762</t>
+          <t>74974</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>109447</t>
+          <t>106051</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>104273</t>
+          <t>105177</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>131652</t>
+          <t>132449</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>188445</t>
+          <t>186935</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>229560</t>
+          <t>229486</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,62%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15611</t>
+          <t>15811</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33119</t>
+          <t>34348</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13566</t>
+          <t>13625</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25118</t>
+          <t>25439</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32299</t>
+          <t>32565</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54243</t>
+          <t>53942</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>624421</t>
+          <t>626249</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>971275</t>
+          <t>980533</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>410770</t>
+          <t>411005</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>464226</t>
+          <t>462080</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1049159</t>
+          <t>1048253</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1513806</t>
+          <t>1542822</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>71,98%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>158370</t>
+          <t>155791</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>414135</t>
+          <t>416912</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>311691</t>
+          <t>315098</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>362498</t>
+          <t>363029</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>427591</t>
+          <t>405530</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>759051</t>
+          <t>759869</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,45%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49633</t>
+          <t>45684</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>131633</t>
+          <t>127219</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141284</t>
+          <t>139166</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>178116</t>
+          <t>176385</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>172764</t>
+          <t>169967</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>295540</t>
+          <t>300355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8651</t>
+          <t>8535</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31163</t>
+          <t>30891</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14236</t>
+          <t>13629</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28109</t>
+          <t>28019</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25541</t>
+          <t>24737</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>53653</t>
+          <t>53110</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>339390</t>
+          <t>344592</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>405264</t>
+          <t>407424</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>381068</t>
+          <t>382093</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>730392</t>
+          <t>722108</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>767462</t>
+          <t>767303</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1168813</t>
+          <t>1149161</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>70,35%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>215770</t>
+          <t>215193</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275334</t>
+          <t>274190</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>157902</t>
+          <t>163465</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>440557</t>
+          <t>440395</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>354830</t>
+          <t>367675</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>677555</t>
+          <t>679666</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,61%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55145</t>
+          <t>56307</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89194</t>
+          <t>90491</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35479</t>
+          <t>37878</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>105732</t>
+          <t>104214</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93150</t>
+          <t>94512</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>179920</t>
+          <t>179301</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5416</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27352</t>
+          <t>27965</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17511</t>
+          <t>17205</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12296</t>
+          <t>12453</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39067</t>
+          <t>41089</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>378018</t>
+          <t>378862</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>441792</t>
+          <t>442594</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>304096</t>
+          <t>315916</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>421889</t>
+          <t>423040</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>697238</t>
+          <t>692824</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>846077</t>
+          <t>846343</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,92%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>340002</t>
+          <t>342254</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>403520</t>
+          <t>404481</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>450096</t>
+          <t>451161</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>608366</t>
+          <t>615186</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>812895</t>
+          <t>811645</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1008172</t>
+          <t>1018962</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>50,47%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>106855</t>
+          <t>107872</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>148194</t>
+          <t>150646</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>142522</t>
+          <t>140463</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>204188</t>
+          <t>205532</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>266232</t>
+          <t>267019</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>340767</t>
+          <t>338302</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12278</t>
+          <t>12344</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27910</t>
+          <t>28454</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19903</t>
+          <t>19424</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38224</t>
+          <t>38147</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35084</t>
+          <t>36239</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>60174</t>
+          <t>61140</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1680746</t>
+          <t>1679159</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2203223</t>
+          <t>2173471</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1465798</t>
+          <t>1467580</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2018492</t>
+          <t>2037453</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3188875</t>
+          <t>3194979</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3900777</t>
+          <t>3926612</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>55,32%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>877855</t>
+          <t>907561</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1267016</t>
+          <t>1271478</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1161807</t>
+          <t>1160249</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1552222</t>
+          <t>1560092</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2269600</t>
+          <t>2268320</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2790536</t>
+          <t>2792173</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,34%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>296365</t>
+          <t>303709</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>432440</t>
+          <t>430218</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>433337</t>
+          <t>429833</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>581781</t>
+          <t>585367</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>790006</t>
+          <t>794288</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>992459</t>
+          <t>993940</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>55565</t>
+          <t>54502</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>95790</t>
+          <t>95683</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>60668</t>
+          <t>60968</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>90459</t>
+          <t>93158</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>126868</t>
+          <t>126612</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>177960</t>
+          <t>178790</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57B2_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P57B2_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>291505</t>
+          <t>311663</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>266015</t>
+          <t>282749</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>319953</t>
+          <t>341675</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>279081</t>
+          <t>304386</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>259462</t>
+          <t>281816</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>300611</t>
+          <t>327592</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>570585</t>
+          <t>616048</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>537907</t>
+          <t>580512</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>606901</t>
+          <t>653165</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,19%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>223904</t>
+          <t>249507</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>199756</t>
+          <t>221806</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>249486</t>
+          <t>275493</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>257798</t>
+          <t>280932</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>238098</t>
+          <t>261381</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>275698</t>
+          <t>300969</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>481702</t>
+          <t>530438</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>451168</t>
+          <t>495304</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>512366</t>
+          <t>564574</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,92%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>90419</t>
+          <t>97291</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>74974</t>
+          <t>81224</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>106051</t>
+          <t>115665</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>117691</t>
+          <t>125328</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>105177</t>
+          <t>108296</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>132449</t>
+          <t>139993</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>208110</t>
+          <t>222619</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>186935</t>
+          <t>200498</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>229486</t>
+          <t>247842</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23258</t>
+          <t>25188</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15811</t>
+          <t>17119</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34348</t>
+          <t>35824</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18635</t>
+          <t>19848</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13625</t>
+          <t>14336</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25439</t>
+          <t>27113</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,22 +1134,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>41892</t>
+          <t>45036</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32565</t>
+          <t>35309</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53942</t>
+          <t>59025</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>629086</t>
+          <t>683649</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>629086</t>
+          <t>683649</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>629086</t>
+          <t>683649</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>673204</t>
+          <t>730493</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>673204</t>
+          <t>730493</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>673204</t>
+          <t>730493</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1302289</t>
+          <t>1414141</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1302289</t>
+          <t>1414141</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1302289</t>
+          <t>1414141</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>752571</t>
+          <t>560071</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>626249</t>
+          <t>522794</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>980533</t>
+          <t>591325</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>436631</t>
+          <t>485424</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>411005</t>
+          <t>454691</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>462080</t>
+          <t>514582</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1189202</t>
+          <t>1045495</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1048253</t>
+          <t>995852</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1542822</t>
+          <t>1088188</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>51,54%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>320588</t>
+          <t>352104</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>155791</t>
+          <t>321748</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>416912</t>
+          <t>387538</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>339276</t>
+          <t>380912</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>315098</t>
+          <t>353255</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>363029</t>
+          <t>406786</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>659865</t>
+          <t>733016</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>405530</t>
+          <t>692429</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>759869</t>
+          <t>778010</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>36,85%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>96378</t>
+          <t>110880</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45684</t>
+          <t>93337</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>127219</t>
+          <t>132870</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>158667</t>
+          <t>178439</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>139166</t>
+          <t>159688</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>176385</t>
+          <t>200490</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>255045</t>
+          <t>289319</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>169967</t>
+          <t>261595</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>300355</t>
+          <t>319905</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19200</t>
+          <t>21288</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8535</t>
+          <t>13663</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30891</t>
+          <t>33140</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20077</t>
+          <t>22290</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13629</t>
+          <t>15493</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28019</t>
+          <t>30223</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>39277</t>
+          <t>43577</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24737</t>
+          <t>33155</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>53110</t>
+          <t>57054</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1188738</t>
+          <t>1044342</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1188738</t>
+          <t>1044342</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1188738</t>
+          <t>1044342</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>954651</t>
+          <t>1067065</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>954651</t>
+          <t>1067065</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>954651</t>
+          <t>1067065</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2143389</t>
+          <t>2111407</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2143389</t>
+          <t>2111407</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2143389</t>
+          <t>2111407</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>375693</t>
+          <t>416941</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>344592</t>
+          <t>382471</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>407424</t>
+          <t>447311</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>513518</t>
+          <t>360719</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>382093</t>
+          <t>332480</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>722108</t>
+          <t>385982</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>889211</t>
+          <t>777660</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>767303</t>
+          <t>734060</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1149161</t>
+          <t>821127</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>50,99%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>243761</t>
+          <t>289016</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>215193</t>
+          <t>259192</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>274190</t>
+          <t>322087</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>330575</t>
+          <t>344383</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>163465</t>
+          <t>317977</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>440395</t>
+          <t>370215</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>574336</t>
+          <t>633399</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>367675</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>679666</t>
+          <t>676624</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>42,02%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>71228</t>
+          <t>83019</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56307</t>
+          <t>67005</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>90491</t>
+          <t>103388</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>76325</t>
+          <t>93469</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37878</t>
+          <t>78118</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>104214</t>
+          <t>112257</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>147553</t>
+          <t>176488</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>94512</t>
+          <t>153394</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>179301</t>
+          <t>201259</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12391</t>
+          <t>12244</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5556</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27965</t>
+          <t>25870</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10019</t>
+          <t>10620</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17205</t>
+          <t>16762</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>22410</t>
+          <t>22864</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12453</t>
+          <t>14180</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41089</t>
+          <t>38967</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>703073</t>
+          <t>801220</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>703073</t>
+          <t>801220</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>703073</t>
+          <t>801220</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>930437</t>
+          <t>809191</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>930437</t>
+          <t>809191</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>930437</t>
+          <t>809191</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1633510</t>
+          <t>1610411</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1633510</t>
+          <t>1610411</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1633510</t>
+          <t>1610411</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>409042</t>
+          <t>434227</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>378862</t>
+          <t>400849</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>442594</t>
+          <t>471196</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>384457</t>
+          <t>425827</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>315916</t>
+          <t>398654</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>423040</t>
+          <t>455471</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>793499</t>
+          <t>860054</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>692824</t>
+          <t>817456</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>846343</t>
+          <t>905251</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>42,99%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>370506</t>
+          <t>398252</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>342254</t>
+          <t>363292</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>404481</t>
+          <t>430638</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>501526</t>
+          <t>467259</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>451161</t>
+          <t>436936</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>615186</t>
+          <t>494564</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>872032</t>
+          <t>865511</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>811645</t>
+          <t>817748</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1018962</t>
+          <t>909684</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>43,2%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>126801</t>
+          <t>136419</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>107872</t>
+          <t>114363</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>150646</t>
+          <t>158116</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>179332</t>
+          <t>192992</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>140463</t>
+          <t>172710</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>205532</t>
+          <t>215004</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>306133</t>
+          <t>329411</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>267019</t>
+          <t>301072</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>338302</t>
+          <t>364441</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>18860</t>
+          <t>19441</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12344</t>
+          <t>12673</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28454</t>
+          <t>29417</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>28329</t>
+          <t>31117</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19424</t>
+          <t>22631</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38147</t>
+          <t>40953</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>47189</t>
+          <t>50558</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36239</t>
+          <t>39506</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61140</t>
+          <t>63596</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>925209</t>
+          <t>988339</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>925209</t>
+          <t>988339</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>925209</t>
+          <t>988339</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1093644</t>
+          <t>1117195</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1093644</t>
+          <t>1117195</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1093644</t>
+          <t>1117195</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2018853</t>
+          <t>2105534</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2018853</t>
+          <t>2105534</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2018853</t>
+          <t>2105534</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1828811</t>
+          <t>1722901</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1679159</t>
+          <t>1650404</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2173471</t>
+          <t>1789014</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1613686</t>
+          <t>1576356</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1467580</t>
+          <t>1523413</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2037453</t>
+          <t>1639012</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>3442497</t>
+          <t>3299257</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3194979</t>
+          <t>3211076</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3926612</t>
+          <t>3385745</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>46,75%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1158759</t>
+          <t>1288878</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>907561</t>
+          <t>1231686</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1271478</t>
+          <t>1355857</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1429176</t>
+          <t>1473485</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1160249</t>
+          <t>1415883</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1560092</t>
+          <t>1525100</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2587934</t>
+          <t>2762363</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2268320</t>
+          <t>2680085</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2792173</t>
+          <t>2842346</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,25%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>384827</t>
+          <t>427608</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>303709</t>
+          <t>390934</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>430218</t>
+          <t>469130</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>532014</t>
+          <t>590228</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>429833</t>
+          <t>555382</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>585367</t>
+          <t>631569</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>916841</t>
+          <t>1017836</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>794288</t>
+          <t>969029</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>993940</t>
+          <t>1071633</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>73709</t>
+          <t>78161</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>54502</t>
+          <t>59741</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>95683</t>
+          <t>96405</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>77060</t>
+          <t>83875</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>60968</t>
+          <t>68427</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>93158</t>
+          <t>99560</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>150768</t>
+          <t>162036</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>126612</t>
+          <t>140982</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>178790</t>
+          <t>185781</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3446105</t>
+          <t>3517549</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3446105</t>
+          <t>3517549</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3446105</t>
+          <t>3517549</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3651936</t>
+          <t>3723944</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3651936</t>
+          <t>3723944</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3651936</t>
+          <t>3723944</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7098041</t>
+          <t>7241493</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7098041</t>
+          <t>7241493</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7098041</t>
+          <t>7241493</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
